--- a/registration_forms/026_e_commerce_ux_design_study_registration--registration_forms.xlsx
+++ b/registration_forms/026_e_commerce_ux_design_study_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mr.',_'value':_1}</t>
+          <t>mr.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mr.', 'value': 1}</t>
+          <t>Mr.</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mrs.',_'value':_2}</t>
+          <t>mrs.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mrs.', 'value': 2}</t>
+          <t>Mrs.</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'dr.',_'value':_3}</t>
+          <t>dr.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Dr.', 'value': 3}</t>
+          <t>Dr.</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1', 'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2', 'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3',_'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3', 'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'option_4',_'value':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Option 4', 'value': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'option_5',_'value':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Option 5', 'value': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'option_2',_'value':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Option 2', 'value': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'option_3',_'value':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Option 3', 'value': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'option_4',_'value':_4}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Option 4', 'value': 4}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
